--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/update-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/update-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="80">
   <si>
     <t>Statement: ExerciseRepository.update(id, data) – updates existing exercise metadata.</t>
   </si>
@@ -136,85 +136,52 @@
     <t>ID length</t>
   </si>
   <si>
+    <t>id = "" (empty)</t>
+  </si>
+  <si>
+    <t>id = "a" (inexistent)</t>
+  </si>
+  <si>
+    <t>id = "a" (existing)</t>
+  </si>
+  <si>
+    <t>Update fields</t>
+  </si>
+  <si>
+    <t>name undef/empty/onechar</t>
+  </si>
+  <si>
+    <t>description undef/empty/onechar</t>
+  </si>
+  <si>
+    <t>muscleGroup variants + undef</t>
+  </si>
+  <si>
+    <t>equipmentNeeded variants + undef</t>
+  </si>
+  <si>
+    <t>BVA</t>
+  </si>
+  <si>
+    <t>BVA-1 EmptyID</t>
+  </si>
+  <si>
     <t>id = ""</t>
   </si>
   <si>
-    <t>id = "a"</t>
-  </si>
-  <si>
-    <t>Name field</t>
-  </si>
-  <si>
-    <t>name = undefined</t>
-  </si>
-  <si>
-    <t>name = ""</t>
-  </si>
-  <si>
-    <t>name = "a"</t>
-  </si>
-  <si>
-    <t>Description field</t>
-  </si>
-  <si>
-    <t>description = undefined</t>
-  </si>
-  <si>
-    <t>description = ""</t>
-  </si>
-  <si>
-    <t>description = "a"</t>
-  </si>
-  <si>
-    <t>MuscleGroup field</t>
-  </si>
-  <si>
-    <t>muscleGroup = undefined</t>
-  </si>
-  <si>
-    <t>muscleGroup = CHEST</t>
-  </si>
-  <si>
-    <t>muscleGroup = SHOULDERS</t>
-  </si>
-  <si>
-    <t>muscleGroup = ARMS</t>
-  </si>
-  <si>
-    <t>muscleGroup = BACK</t>
-  </si>
-  <si>
-    <t>muscleGroup = CORE</t>
-  </si>
-  <si>
-    <t>muscleGroup = LEGS</t>
-  </si>
-  <si>
-    <t>Equipment field</t>
-  </si>
-  <si>
-    <t>equipmentNeeded = undefined</t>
-  </si>
-  <si>
-    <t>equipmentNeeded = CABLE</t>
-  </si>
-  <si>
-    <t>equipmentNeeded = DUMBBELL</t>
-  </si>
-  <si>
-    <t>equipmentNeeded = BARBELL</t>
-  </si>
-  <si>
-    <t>equipmentNeeded = MACHINE</t>
-  </si>
-  <si>
-    <t>BVA</t>
-  </si>
-  <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>BVA-2 OneCharID</t>
+    <t>BVA-2 InexChar</t>
+  </si>
+  <si>
+    <t>id = "a" (inex)</t>
+  </si>
+  <si>
+    <t>BVA-3 ExistChar</t>
+  </si>
+  <si>
+    <t>id = "a" (exist)</t>
+  </si>
+  <si>
+    <t>Updates successfully</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -244,55 +211,10 @@
     <t>BVA-3</t>
   </si>
   <si>
-    <t>Updates successfully</t>
-  </si>
-  <si>
-    <t>BVA-4</t>
-  </si>
-  <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>BVA-7</t>
-  </si>
-  <si>
-    <t>BVA-8</t>
-  </si>
-  <si>
-    <t>BVA-9</t>
-  </si>
-  <si>
-    <t>BVA-10</t>
-  </si>
-  <si>
-    <t>BVA-11</t>
-  </si>
-  <si>
-    <t>BVA-12</t>
-  </si>
-  <si>
-    <t>BVA-13</t>
-  </si>
-  <si>
-    <t>BVA-14</t>
-  </si>
-  <si>
-    <t>BVA-15</t>
-  </si>
-  <si>
-    <t>BVA-16</t>
-  </si>
-  <si>
-    <t>BVA-17</t>
-  </si>
-  <si>
-    <t>BVA-18</t>
-  </si>
-  <si>
-    <t>BVA-19</t>
+    <t>Various field values</t>
+  </si>
+  <si>
+    <t>Success</t>
   </si>
   <si>
     <t>Testing</t>
@@ -1022,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1068,10 +990,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,7 +1001,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>43</v>
@@ -1101,10 +1023,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1115,150 +1037,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1269,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1284,7 +1063,7 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>23</v>
@@ -1301,10 +1080,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
@@ -1318,15 +1097,32 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1338,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1354,10 +1150,10 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>23</v>
@@ -1380,10 +1176,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>29</v>
@@ -1400,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>32</v>
@@ -1420,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>35</v>
@@ -1437,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>32</v>
@@ -1457,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>40</v>
@@ -1477,13 +1273,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>29</v>
@@ -1497,13 +1293,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>29</v>
@@ -1517,13 +1313,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>29</v>
@@ -1537,13 +1333,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>29</v>
@@ -1557,13 +1353,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>29</v>
@@ -1577,13 +1373,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>29</v>
@@ -1597,13 +1393,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>29</v>
@@ -1617,13 +1413,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>29</v>
@@ -1637,13 +1433,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>29</v>
@@ -1657,13 +1453,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>29</v>
@@ -1677,13 +1473,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>29</v>
@@ -1697,13 +1493,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>29</v>
@@ -1717,13 +1513,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>29</v>
@@ -1737,13 +1533,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>29</v>
@@ -1757,13 +1553,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>29</v>
@@ -1777,13 +1573,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>29</v>
@@ -1797,15 +1593,55 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1834,16 +1670,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1851,45 +1687,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1898,19 +1734,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/update-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/update-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="80">
-  <si>
-    <t>Statement: ExerciseRepository.update(id, data) – updates existing exercise metadata.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="128">
+  <si>
+    <t>Statement: ExerciseRepository.update(id, data) – Updates an existing exercise record. Returns the updated Exercise on success. Throws NotFoundError("Exercise not found") if no exercise exists with the given ID. Throws ConflictError("Exercise name already in use") if the new name is already taken by a different exercise.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: id: string, data: UpdateExerciseInput</t>
+    <t>Input: id: string, data: UpdateExerciseInput { name?, description?, muscleGroup?, equipmentNeeded? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. An exercise with the given ID may or may not exist. Any new name may or may not already be registered to a different exercise.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;Exercise&gt; | throws NotFoundError/ConflictError</t>
+    <t>Output: Promise&lt;Exercise&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Updates record or throws NotFoundError/ConflictError.</t>
+    <t>On success: Exercise returned with updated fields (result.name, result.description, result.muscleGroup, result.equipmentNeeded, result.id). On failure: NotFoundError or ConflictError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,19 +67,19 @@
     <t>Exercise existence</t>
   </si>
   <si>
-    <t>Found</t>
-  </si>
-  <si>
-    <t>Not found (NotFoundError)</t>
+    <t>Existing ID + valid data → Exercise returned with result.name: "Updated Bench Press", result equal to expectedReturn</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError("Exercise not found")</t>
   </si>
   <si>
     <t>Name uniqueness</t>
   </si>
   <si>
-    <t>New name unique or same</t>
-  </si>
-  <si>
-    <t>New name taken (ConflictError)</t>
+    <t>New name not taken by another exercise → Exercise returned</t>
+  </si>
+  <si>
+    <t>Name taken by a different exercise → ConflictError("Exercise name already in use")</t>
   </si>
   <si>
     <t>No TC</t>
@@ -97,13 +97,13 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-3</t>
-  </si>
-  <si>
-    <t>Exist, valid unique name</t>
-  </si>
-  <si>
-    <t>Returns updated Exercise</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { name: "Updated Bench Press" } (exercise exists, new name not taken)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.name: "Updated Bench Press", result equal to expectedReturn</t>
   </si>
   <si>
     <t>Passed</t>
@@ -112,19 +112,19 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Non-existent ID</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>id: "non-existent-id", data: { description: "New description" } (no exercise with that ID)</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Exercise not found")</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Name conflict with other</t>
-  </si>
-  <si>
-    <t>Throws ConflictError</t>
+    <t>id: EXERCISE_ID, data: { name: "Existing Exercise" } (exercise exists, name taken by a different exercise)</t>
+  </si>
+  <si>
+    <t>throws ConflictError("Exercise name already in use")</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -133,55 +133,211 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>ID length</t>
-  </si>
-  <si>
-    <t>id = "" (empty)</t>
-  </si>
-  <si>
-    <t>id = "a" (inexistent)</t>
-  </si>
-  <si>
-    <t>id = "a" (existing)</t>
-  </si>
-  <si>
-    <t>Update fields</t>
-  </si>
-  <si>
-    <t>name undef/empty/onechar</t>
-  </si>
-  <si>
-    <t>description undef/empty/onechar</t>
-  </si>
-  <si>
-    <t>muscleGroup variants + undef</t>
-  </si>
-  <si>
-    <t>equipmentNeeded variants + undef</t>
+    <t>Exercise ID length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>name field</t>
+  </si>
+  <si>
+    <t>name: undefined, name: "" (empty), name: "a" (one char)</t>
+  </si>
+  <si>
+    <t>description field</t>
+  </si>
+  <si>
+    <t>description: undefined, description: "" (empty), description: "a" (one char)</t>
+  </si>
+  <si>
+    <t>muscleGroup field</t>
+  </si>
+  <si>
+    <t>muscleGroup: undefined, MuscleGroup.CHEST, MuscleGroup.SHOULDERS, MuscleGroup.ARMS, MuscleGroup.BACK, MuscleGroup.CORE, MuscleGroup.LEGS</t>
+  </si>
+  <si>
+    <t>equipmentNeeded field</t>
+  </si>
+  <si>
+    <t>equipmentNeeded: undefined, Equipment.CABLE, Equipment.DUMBBELL, Equipment.BARBELL, Equipment.MACHINE</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>id = ""</t>
-  </si>
-  <si>
-    <t>BVA-2 InexChar</t>
-  </si>
-  <si>
-    <t>id = "a" (inex)</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistChar</t>
-  </si>
-  <si>
-    <t>id = "a" (exist)</t>
-  </si>
-  <si>
-    <t>Updates successfully</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "" (no exercise with that ID), data: { description: "Updated description" }</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no exercise with that ID), data: { description: "Updated description" }</t>
+  </si>
+  <si>
+    <t>id: "a" (exercise exists with id: "a"), data: { description: "Updated description" }</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.id: "a", result.description: "Updated description"</t>
+  </si>
+  <si>
+    <t>BVA-2 (undef)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { name: undefined } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result equal to { ...MOCK_EXERCISE }</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=0)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { name: "" } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.name: ""</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=1)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { name: "a" } (exercise exists, new name not taken)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.name: "a"</t>
+  </si>
+  <si>
+    <t>BVA-3 (undef)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { description: undefined } (exercise exists)</t>
+  </si>
+  <si>
+    <t>BVA-3 (n=0)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { description: "" } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.description: ""</t>
+  </si>
+  <si>
+    <t>BVA-3 (n=1)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { description: "a" } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.description: "a"</t>
+  </si>
+  <si>
+    <t>BVA-4 (undef)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { muscleGroup: undefined } (exercise exists)</t>
+  </si>
+  <si>
+    <t>BVA-4 (CHEST)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { muscleGroup: MuscleGroup.CHEST } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.muscleGroup: MuscleGroup.CHEST</t>
+  </si>
+  <si>
+    <t>BVA-4 (SHOULDERS)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { muscleGroup: MuscleGroup.SHOULDERS } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.muscleGroup: MuscleGroup.SHOULDERS</t>
+  </si>
+  <si>
+    <t>BVA-4 (ARMS)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { muscleGroup: MuscleGroup.ARMS } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.muscleGroup: MuscleGroup.ARMS</t>
+  </si>
+  <si>
+    <t>BVA-4 (BACK)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { muscleGroup: MuscleGroup.BACK } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.muscleGroup: MuscleGroup.BACK</t>
+  </si>
+  <si>
+    <t>BVA-4 (CORE)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { muscleGroup: MuscleGroup.CORE } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.muscleGroup: MuscleGroup.CORE</t>
+  </si>
+  <si>
+    <t>BVA-4 (LEGS)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { muscleGroup: MuscleGroup.LEGS } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.muscleGroup: MuscleGroup.LEGS</t>
+  </si>
+  <si>
+    <t>BVA-5 (undef)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { equipmentNeeded: undefined } (exercise exists)</t>
+  </si>
+  <si>
+    <t>BVA-5 (CABLE)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { equipmentNeeded: Equipment.CABLE } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.equipmentNeeded: Equipment.CABLE</t>
+  </si>
+  <si>
+    <t>BVA-5 (DUMBBELL)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { equipmentNeeded: Equipment.DUMBBELL } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.equipmentNeeded: Equipment.DUMBBELL</t>
+  </si>
+  <si>
+    <t>BVA-5 (BARBELL)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { equipmentNeeded: Equipment.BARBELL } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.equipmentNeeded: Equipment.BARBELL</t>
+  </si>
+  <si>
+    <t>BVA-5 (MACHINE)</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, data: { equipmentNeeded: Equipment.MACHINE } (exercise exists)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.equipmentNeeded: Equipment.MACHINE</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -190,18 +346,6 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Existing ID, unique new name</t>
-  </si>
-  <si>
-    <t>Exercise name updated</t>
-  </si>
-  <si>
-    <t>Non-existent exercise ID</t>
-  </si>
-  <si>
-    <t>Name taken by another record</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
@@ -211,10 +355,10 @@
     <t>BVA-3</t>
   </si>
   <si>
-    <t>Various field values</t>
-  </si>
-  <si>
-    <t>Success</t>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
   </si>
   <si>
     <t>Testing</t>
@@ -247,7 +391,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-03</t>
+    <t>REPO-16</t>
   </si>
   <si>
     <t>n/a</t>
@@ -813,7 +957,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -841,7 +985,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -944,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -979,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -990,10 +1134,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1001,10 +1145,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1012,32 +1156,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1048,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1063,7 +1185,7 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>23</v>
@@ -1080,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>29</v>
@@ -1097,13 +1219,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>29</v>
@@ -1117,12 +1239,318 @@
         <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1150,10 +1578,10 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>23</v>
@@ -1176,10 +1604,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>29</v>
@@ -1196,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>32</v>
@@ -1216,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>35</v>
@@ -1233,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>29</v>
@@ -1253,13 +1681,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>29</v>
@@ -1273,13 +1701,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>29</v>
@@ -1293,13 +1721,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>29</v>
@@ -1313,13 +1741,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>29</v>
@@ -1333,13 +1761,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>29</v>
@@ -1353,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>29</v>
@@ -1373,13 +1801,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>29</v>
@@ -1393,13 +1821,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>29</v>
@@ -1413,13 +1841,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>29</v>
@@ -1433,13 +1861,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>29</v>
@@ -1453,13 +1881,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>29</v>
@@ -1473,13 +1901,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>29</v>
@@ -1493,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>29</v>
@@ -1513,13 +1941,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>29</v>
@@ -1533,13 +1961,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>29</v>
@@ -1553,13 +1981,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>29</v>
@@ -1573,13 +2001,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>29</v>
@@ -1593,13 +2021,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>29</v>
@@ -1613,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>29</v>
@@ -1633,13 +2061,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>29</v>
@@ -1670,16 +2098,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1687,39 +2115,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="B3" s="1">
         <v>24</v>
@@ -1734,19 +2162,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
